--- a/final_data_pipeline/output/325311longform.xlsx
+++ b/final_data_pipeline/output/325311longform.xlsx
@@ -1029,7 +1029,7 @@
         <v>153</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -1118,7 +1118,7 @@
         <v>154</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1207,7 +1207,7 @@
         <v>153</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1296,7 +1296,7 @@
         <v>153</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1385,7 +1385,7 @@
         <v>154</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1474,7 +1474,7 @@
         <v>154</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1563,7 +1563,7 @@
         <v>153</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1652,7 +1652,7 @@
         <v>154</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1741,7 +1741,7 @@
         <v>153</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1830,7 +1830,7 @@
         <v>153</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1919,7 +1919,7 @@
         <v>154</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -2008,7 +2008,7 @@
         <v>154</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -3699,7 +3699,7 @@
         <v>153</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3788,7 +3788,7 @@
         <v>153</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3877,7 +3877,7 @@
         <v>153</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -3966,7 +3966,7 @@
         <v>154</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -4055,7 +4055,7 @@
         <v>154</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB36">
         <v>8000</v>
@@ -4144,7 +4144,7 @@
         <v>154</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -13311,7 +13311,7 @@
         <v>154</v>
       </c>
       <c r="AA140">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB140">
         <v>8000</v>
@@ -13400,7 +13400,7 @@
         <v>154</v>
       </c>
       <c r="AA141">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB141">
         <v>8000</v>
@@ -13489,7 +13489,7 @@
         <v>153</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -13578,7 +13578,7 @@
         <v>154</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -13667,7 +13667,7 @@
         <v>153</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -13756,7 +13756,7 @@
         <v>154</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -13845,7 +13845,7 @@
         <v>153</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -13934,7 +13934,7 @@
         <v>154</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -14023,7 +14023,7 @@
         <v>153</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -14112,7 +14112,7 @@
         <v>153</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -14201,7 +14201,7 @@
         <v>153</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -14290,7 +14290,7 @@
         <v>154</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -17049,7 +17049,7 @@
         <v>153</v>
       </c>
       <c r="AA182">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB182">
         <v>8000</v>
@@ -17141,7 +17141,7 @@
         <v>153</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB183">
         <v>8000</v>
@@ -17230,7 +17230,7 @@
         <v>153</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB184">
         <v>8000</v>
@@ -17319,7 +17319,7 @@
         <v>154</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB185">
         <v>8000</v>
@@ -17408,7 +17408,7 @@
         <v>153</v>
       </c>
       <c r="AA186">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB186">
         <v>8000</v>
@@ -17497,7 +17497,7 @@
         <v>154</v>
       </c>
       <c r="AA187">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB187">
         <v>8000</v>
@@ -17586,7 +17586,7 @@
         <v>154</v>
       </c>
       <c r="AA188">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB188">
         <v>8000</v>
@@ -17675,7 +17675,7 @@
         <v>154</v>
       </c>
       <c r="AA189">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB189">
         <v>8000</v>
@@ -17764,7 +17764,7 @@
         <v>153</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB190">
         <v>8000</v>
@@ -17853,7 +17853,7 @@
         <v>153</v>
       </c>
       <c r="AA191">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB191">
         <v>8000</v>
@@ -17942,7 +17942,7 @@
         <v>153</v>
       </c>
       <c r="AA192">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB192">
         <v>8000</v>
@@ -18031,7 +18031,7 @@
         <v>154</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB193">
         <v>8000</v>
@@ -18120,7 +18120,7 @@
         <v>154</v>
       </c>
       <c r="AA194">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB194">
         <v>8000</v>
@@ -19277,7 +19277,7 @@
         <v>153</v>
       </c>
       <c r="AA207">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB207">
         <v>8000</v>
@@ -19366,7 +19366,7 @@
         <v>153</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB208">
         <v>8000</v>
@@ -19458,7 +19458,7 @@
         <v>153</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB209">
         <v>8000</v>
@@ -19547,7 +19547,7 @@
         <v>153</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB210">
         <v>8000</v>
@@ -19636,7 +19636,7 @@
         <v>154</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB211">
         <v>8000</v>
@@ -19725,7 +19725,7 @@
         <v>154</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB212">
         <v>8000</v>
@@ -19814,7 +19814,7 @@
         <v>154</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB213">
         <v>8000</v>
@@ -20437,7 +20437,7 @@
         <v>154</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB220">
         <v>8000</v>
@@ -20526,7 +20526,7 @@
         <v>154</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB221">
         <v>8000</v>
@@ -20615,7 +20615,7 @@
         <v>153</v>
       </c>
       <c r="AA222">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB222">
         <v>8000</v>
@@ -20704,7 +20704,7 @@
         <v>153</v>
       </c>
       <c r="AA223">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB223">
         <v>8000</v>
@@ -20793,7 +20793,7 @@
         <v>154</v>
       </c>
       <c r="AA224">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB224">
         <v>8000</v>
@@ -20882,7 +20882,7 @@
         <v>153</v>
       </c>
       <c r="AA225">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB225">
         <v>8000</v>
@@ -22039,7 +22039,7 @@
         <v>154</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB238">
         <v>8000</v>
@@ -22128,7 +22128,7 @@
         <v>154</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB239">
         <v>8000</v>
@@ -22217,7 +22217,7 @@
         <v>154</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB240">
         <v>8000</v>
@@ -22306,7 +22306,7 @@
         <v>154</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB241">
         <v>8000</v>
@@ -22395,7 +22395,7 @@
         <v>154</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB242">
         <v>8000</v>
@@ -22484,7 +22484,7 @@
         <v>154</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB243">
         <v>8000</v>
@@ -22573,7 +22573,7 @@
         <v>154</v>
       </c>
       <c r="AA244">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB244">
         <v>8000</v>
@@ -22662,7 +22662,7 @@
         <v>154</v>
       </c>
       <c r="AA245">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB245">
         <v>8000</v>
@@ -22751,7 +22751,7 @@
         <v>154</v>
       </c>
       <c r="AA246">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB246">
         <v>8000</v>
@@ -22840,7 +22840,7 @@
         <v>153</v>
       </c>
       <c r="AA247">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB247">
         <v>8000</v>
@@ -22929,7 +22929,7 @@
         <v>153</v>
       </c>
       <c r="AA248">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB248">
         <v>8000</v>
@@ -23018,7 +23018,7 @@
         <v>153</v>
       </c>
       <c r="AA249">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB249">
         <v>8000</v>
@@ -23107,7 +23107,7 @@
         <v>153</v>
       </c>
       <c r="AA250">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB250">
         <v>8000</v>
@@ -23196,7 +23196,7 @@
         <v>153</v>
       </c>
       <c r="AA251">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB251">
         <v>8000</v>
@@ -23285,7 +23285,7 @@
         <v>154</v>
       </c>
       <c r="AA252">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB252">
         <v>8000</v>
@@ -23374,7 +23374,7 @@
         <v>154</v>
       </c>
       <c r="AA253">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB253">
         <v>8000</v>
@@ -23463,7 +23463,7 @@
         <v>153</v>
       </c>
       <c r="AA254">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB254">
         <v>8000</v>
@@ -23552,7 +23552,7 @@
         <v>154</v>
       </c>
       <c r="AA255">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB255">
         <v>8000</v>
@@ -23641,7 +23641,7 @@
         <v>153</v>
       </c>
       <c r="AA256">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB256">
         <v>8000</v>
@@ -23730,7 +23730,7 @@
         <v>153</v>
       </c>
       <c r="AA257">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB257">
         <v>8000</v>
@@ -23819,7 +23819,7 @@
         <v>154</v>
       </c>
       <c r="AA258">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB258">
         <v>8000</v>
@@ -23908,7 +23908,7 @@
         <v>153</v>
       </c>
       <c r="AA259">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB259">
         <v>8000</v>
@@ -23997,7 +23997,7 @@
         <v>153</v>
       </c>
       <c r="AA260">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB260">
         <v>8000</v>
@@ -24086,7 +24086,7 @@
         <v>154</v>
       </c>
       <c r="AA261">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB261">
         <v>8000</v>
@@ -24175,7 +24175,7 @@
         <v>153</v>
       </c>
       <c r="AA262">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB262">
         <v>8000</v>
@@ -24264,7 +24264,7 @@
         <v>153</v>
       </c>
       <c r="AA263">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB263">
         <v>8000</v>
@@ -24353,7 +24353,7 @@
         <v>153</v>
       </c>
       <c r="AA264">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB264">
         <v>8000</v>
@@ -24442,7 +24442,7 @@
         <v>153</v>
       </c>
       <c r="AA265">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB265">
         <v>8000</v>
@@ -24531,7 +24531,7 @@
         <v>153</v>
       </c>
       <c r="AA266">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB266">
         <v>8000</v>
@@ -24620,7 +24620,7 @@
         <v>153</v>
       </c>
       <c r="AA267">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB267">
         <v>8000</v>
@@ -24709,7 +24709,7 @@
         <v>153</v>
       </c>
       <c r="AA268">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB268">
         <v>8000</v>
@@ -24798,7 +24798,7 @@
         <v>154</v>
       </c>
       <c r="AA269">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB269">
         <v>8000</v>
@@ -24887,7 +24887,7 @@
         <v>154</v>
       </c>
       <c r="AA270">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB270">
         <v>8000</v>
@@ -24976,7 +24976,7 @@
         <v>154</v>
       </c>
       <c r="AA271">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB271">
         <v>8000</v>
@@ -25065,7 +25065,7 @@
         <v>153</v>
       </c>
       <c r="AA272">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB272">
         <v>8000</v>
@@ -25154,7 +25154,7 @@
         <v>154</v>
       </c>
       <c r="AA273">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB273">
         <v>8000</v>
@@ -25777,7 +25777,7 @@
         <v>153</v>
       </c>
       <c r="AA280">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB280">
         <v>8000</v>
@@ -25866,7 +25866,7 @@
         <v>154</v>
       </c>
       <c r="AA281">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB281">
         <v>8000</v>
@@ -25955,7 +25955,7 @@
         <v>153</v>
       </c>
       <c r="AA282">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB282">
         <v>8000</v>
@@ -26044,7 +26044,7 @@
         <v>153</v>
       </c>
       <c r="AA283">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB283">
         <v>8000</v>
@@ -26133,7 +26133,7 @@
         <v>154</v>
       </c>
       <c r="AA284">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB284">
         <v>8000</v>
@@ -26222,7 +26222,7 @@
         <v>154</v>
       </c>
       <c r="AA285">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB285">
         <v>8000</v>
@@ -27379,7 +27379,7 @@
         <v>153</v>
       </c>
       <c r="AA298">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB298">
         <v>8000</v>
@@ -27468,7 +27468,7 @@
         <v>153</v>
       </c>
       <c r="AA299">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB299">
         <v>8000</v>
@@ -27557,7 +27557,7 @@
         <v>154</v>
       </c>
       <c r="AA300">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB300">
         <v>8000</v>
@@ -27646,7 +27646,7 @@
         <v>154</v>
       </c>
       <c r="AA301">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB301">
         <v>8000</v>
@@ -27735,7 +27735,7 @@
         <v>153</v>
       </c>
       <c r="AA302">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB302">
         <v>8000</v>
@@ -27824,7 +27824,7 @@
         <v>154</v>
       </c>
       <c r="AA303">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB303">
         <v>8000</v>
@@ -30675,7 +30675,7 @@
         <v>154</v>
       </c>
       <c r="AA335">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB335">
         <v>8000</v>
@@ -30764,7 +30764,7 @@
         <v>154</v>
       </c>
       <c r="AA336">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB336">
         <v>8000</v>
@@ -30853,7 +30853,7 @@
         <v>153</v>
       </c>
       <c r="AA337">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB337">
         <v>8000</v>
@@ -30942,7 +30942,7 @@
         <v>153</v>
       </c>
       <c r="AA338">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB338">
         <v>8000</v>
@@ -31031,7 +31031,7 @@
         <v>153</v>
       </c>
       <c r="AA339">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB339">
         <v>8000</v>
@@ -31120,7 +31120,7 @@
         <v>154</v>
       </c>
       <c r="AA340">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB340">
         <v>8000</v>
@@ -31209,7 +31209,7 @@
         <v>153</v>
       </c>
       <c r="AA341">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB341">
         <v>8000</v>
@@ -31298,7 +31298,7 @@
         <v>153</v>
       </c>
       <c r="AA342">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB342">
         <v>8000</v>
@@ -31387,7 +31387,7 @@
         <v>154</v>
       </c>
       <c r="AA343">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB343">
         <v>8000</v>
@@ -31476,7 +31476,7 @@
         <v>154</v>
       </c>
       <c r="AA344">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB344">
         <v>8000</v>
@@ -31565,7 +31565,7 @@
         <v>154</v>
       </c>
       <c r="AA345">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB345">
         <v>8000</v>
@@ -31654,7 +31654,7 @@
         <v>154</v>
       </c>
       <c r="AA346">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB346">
         <v>8000</v>
@@ -31743,7 +31743,7 @@
         <v>154</v>
       </c>
       <c r="AA347">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB347">
         <v>8000</v>
@@ -31832,7 +31832,7 @@
         <v>153</v>
       </c>
       <c r="AA348">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB348">
         <v>8000</v>
@@ -31924,7 +31924,7 @@
         <v>153</v>
       </c>
       <c r="AA349">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB349">
         <v>8000</v>
@@ -32013,7 +32013,7 @@
         <v>153</v>
       </c>
       <c r="AA350">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB350">
         <v>8000</v>
@@ -32102,7 +32102,7 @@
         <v>153</v>
       </c>
       <c r="AA351">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB351">
         <v>8000</v>
@@ -32191,7 +32191,7 @@
         <v>153</v>
       </c>
       <c r="AA352">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB352">
         <v>8000</v>
@@ -32280,7 +32280,7 @@
         <v>154</v>
       </c>
       <c r="AA353">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB353">
         <v>8000</v>
